--- a/app/reports/PSN_research.xlsx
+++ b/app/reports/PSN_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.844</v>
+        <v>0.795</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>94.67</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>50.71</v>
+        <v>41.3765</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.867</v>
+        <v>0.871</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.708</v>
+        <v>0.642</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.756</v>
+        <v>0.667</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04375999927520752</v>
+        <v>0.05302000045776367</v>
       </c>
     </row>
     <row r="6">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>0.7</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="8">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>1685901952</v>
+        <v>1645378944</v>
       </c>
     </row>
     <row r="33">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>283920992</v>
+        <v>266044000</v>
       </c>
     </row>
     <row r="34">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>106978517.8465786</v>
+        <v>106805391.4661704</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>50.71</v>
+        <v>41.3765</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>5424880640</v>
+        <v>4419233280</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>24.26</v>
+        <v>28.54</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>13.28</v>
+        <v>12.61</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>8463366656</v>
+        <v>7778047488</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>16.374666</v>
+        <v>16.030813</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>11.266</v>
+        <v>10.695</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.35</v>
+        <v>2.203</v>
       </c>
     </row>
     <row r="7">
@@ -1564,20 +1564,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CAE Inc.</t>
+          <t>CAE Inc</t>
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>8107023360</v>
+        <v>7795184640</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>37.07353</v>
+        <v>38.444443</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.974</v>
+        <v>11.3</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.231</v>
+        <v>2.103</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>10109762560</v>
+        <v>10128226304</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>23.509434</v>
+        <v>22.696104</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>15.617</v>
+        <v>15.769</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.801</v>
+        <v>2.896</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>9419377664</v>
+        <v>9362492416</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>27.095587</v>
+        <v>25.753496</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>14.081</v>
+        <v>15.396</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>2.244</v>
+        <v>2.382</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>16423772160</v>
+        <v>12244248576</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>87.18437</v>
+        <v>47.656322</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>33.232</v>
+        <v>21.472</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>4.052</v>
+        <v>3.078</v>
       </c>
     </row>
     <row r="11">
@@ -1660,19 +1660,13 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chart Industries, Inc.</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="n">
-        <v>9999131648</v>
-      </c>
+          <t>GTLS</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="n"/>
       <c r="D11" s="34" t="n"/>
-      <c r="E11" s="34" t="n">
-        <v>16.501</v>
-      </c>
-      <c r="F11" s="34" t="n">
-        <v>3.319</v>
-      </c>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1686,16 +1680,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>14584727552</v>
+        <v>10358891520</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>50.832947</v>
+        <v>32.018517</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>15.912</v>
+        <v>12.084</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>3.186</v>
+        <v>2.429</v>
       </c>
     </row>
     <row r="13">
@@ -1710,16 +1704,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>11851348992</v>
+        <v>8522610176</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>45.175575</v>
+        <v>29.957748</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>24.581</v>
+        <v>17.237</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.162</v>
+        <v>3.633</v>
       </c>
     </row>
     <row r="15">
@@ -1767,10 +1761,10 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E17" s="36" t="n">
         <v>0.4</v>
-      </c>
-      <c r="E17" s="36" t="n">
-        <v>0.333</v>
       </c>
       <c r="F17" s="36" t="n">
         <v>0</v>

--- a/app/reports/PSN_research.xlsx
+++ b/app/reports/PSN_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.795</v>
+        <v>0.796</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>77.40000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>41.3765</v>
+        <v>41.22</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.871</v>
+        <v>0.91</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.642</v>
+        <v>0.645</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05302000045776367</v>
+        <v>0.05217999935150146</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>106805391.4661704</v>
+        <v>106805398.5443959</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>41.3765</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>4419233280</v>
+        <v>4402518528</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>28.54</v>
+        <v>28.43</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>12.61</v>
+        <v>12.48</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>7778047488</v>
+        <v>7654370816</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>16.030813</v>
+        <v>15.77591</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>10.695</v>
+        <v>10.408</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.203</v>
+        <v>2.144</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>7795184640</v>
+        <v>7788748288</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>38.444443</v>
+        <v>38.4127</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.3</v>
+        <v>11.217</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.103</v>
+        <v>2.087</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>10128226304</v>
+        <v>10274273280</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>22.696104</v>
+        <v>23.023376</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>15.769</v>
+        <v>15.725</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.896</v>
+        <v>2.888</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>9362492416</v>
+        <v>9340564480</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>25.753496</v>
+        <v>25.603659</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.396</v>
+        <v>15.274</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>2.382</v>
+        <v>2.363</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>12244248576</v>
+        <v>12300064768</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>47.656322</v>
+        <v>49.11557</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>21.472</v>
+        <v>20.984</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.078</v>
+        <v>3.008</v>
       </c>
     </row>
     <row r="11">
@@ -1680,16 +1680,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>10358891520</v>
+        <v>10478050304</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>32.018517</v>
+        <v>32.45361</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>12.084</v>
+        <v>12.042</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.429</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="13">
@@ -1704,16 +1704,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>8522610176</v>
+        <v>8478283776</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>29.957748</v>
+        <v>29.697369</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>17.237</v>
+        <v>17.135</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>3.633</v>
+        <v>3.611</v>
       </c>
     </row>
     <row r="15">
